--- a/excel/testdata/schema_header_1row/test_cases.xlsx
+++ b/excel/testdata/schema_header_1row/test_cases.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet name="1-row-simple" sheetId="1" r:id="rId1"/>
     <sheet name="1-row-empty-header" sheetId="2" r:id="rId5"/>
-    <sheet name="1-row-line-break" sheetId="3" r:id="rId6"/>
-    <sheet name="1-row-horizontal-merge" sheetId="4" r:id="rId7"/>
+    <sheet name="1-row-empty-header-valid" sheetId="3" r:id="rId6"/>
+    <sheet name="1-row-line-break" sheetId="4" r:id="rId7"/>
+    <sheet name="1-row-horizontal-merge" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>headerA</t>
   </si>
@@ -26,6 +27,42 @@
   </si>
   <si>
     <t>headerC</t>
+  </si>
+  <si>
+    <t>r2cA</t>
+  </si>
+  <si>
+    <t>r3cA</t>
+  </si>
+  <si>
+    <t>r4cA</t>
+  </si>
+  <si>
+    <t>r2cB</t>
+  </si>
+  <si>
+    <t>r3cB</t>
+  </si>
+  <si>
+    <t>r4cB</t>
+  </si>
+  <si>
+    <t>r2cC</t>
+  </si>
+  <si>
+    <t>r3cC</t>
+  </si>
+  <si>
+    <t>r4cC</t>
+  </si>
+  <si>
+    <t>r2cD</t>
+  </si>
+  <si>
+    <t>r3cD</t>
+  </si>
+  <si>
+    <t>r4cD</t>
   </si>
   <si>
     <t>this
@@ -355,6 +392,39 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -374,6 +444,48 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -387,7 +499,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -403,10 +551,92 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
       <c r="D1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
